--- a/artfynd/A 44648-2020 artfynd.xlsx
+++ b/artfynd/A 44648-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44648-2020 artfynd.xlsx
+++ b/artfynd/A 44648-2020 artfynd.xlsx
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117967525</v>
+        <v>117967216</v>
       </c>
       <c r="B26" t="n">
-        <v>57303</v>
+        <v>78480</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,31 +3379,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3411,13 +3406,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>728504</v>
+        <v>728577</v>
       </c>
       <c r="R26" t="n">
-        <v>7172502</v>
+        <v>7172578</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3455,6 +3450,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3473,7 +3469,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117967216</v>
+        <v>117966993</v>
       </c>
       <c r="B27" t="n">
         <v>78480</v>
@@ -3508,7 +3504,11 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>728577</v>
+        <v>728536</v>
       </c>
       <c r="R27" t="n">
-        <v>7172578</v>
+        <v>7172529</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117966993</v>
+        <v>117967525</v>
       </c>
       <c r="B28" t="n">
-        <v>78480</v>
+        <v>57303</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3595,28 +3595,29 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3626,13 +3627,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>728536</v>
+        <v>728504</v>
       </c>
       <c r="R28" t="n">
-        <v>7172529</v>
+        <v>7172502</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3670,7 +3671,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4013,10 +4013,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117966745</v>
+        <v>117966939</v>
       </c>
       <c r="B32" t="n">
-        <v>97753</v>
+        <v>78480</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4025,35 +4025,34 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4061,10 +4060,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>728469</v>
+        <v>728530</v>
       </c>
       <c r="R32" t="n">
-        <v>7172427</v>
+        <v>7172496</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4124,10 +4123,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117966939</v>
+        <v>117967497</v>
       </c>
       <c r="B33" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4140,28 +4139,29 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4171,13 +4171,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>728530</v>
+        <v>728493</v>
       </c>
       <c r="R33" t="n">
-        <v>7172496</v>
+        <v>7172518</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4215,7 +4215,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4234,7 +4233,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117967497</v>
+        <v>117967072</v>
       </c>
       <c r="B34" t="n">
         <v>57287</v>
@@ -4282,13 +4281,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>728493</v>
+        <v>728557</v>
       </c>
       <c r="R34" t="n">
-        <v>7172518</v>
+        <v>7172490</v>
       </c>
       <c r="S34" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4318,6 +4317,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4344,10 +4348,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117967072</v>
+        <v>117966745</v>
       </c>
       <c r="B35" t="n">
-        <v>57287</v>
+        <v>97753</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4356,35 +4360,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4392,10 +4396,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>728557</v>
+        <v>728469</v>
       </c>
       <c r="R35" t="n">
-        <v>7172490</v>
+        <v>7172427</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4430,17 +4434,13 @@
           <t>2024-06-21</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4459,10 +4459,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117967205</v>
+        <v>117965822</v>
       </c>
       <c r="B36" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4475,26 +4475,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4502,10 +4507,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>728625</v>
+        <v>728482</v>
       </c>
       <c r="R36" t="n">
-        <v>7172559</v>
+        <v>7172407</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4546,7 +4551,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4565,10 +4569,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117965822</v>
+        <v>117967205</v>
       </c>
       <c r="B37" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4581,31 +4585,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4613,10 +4612,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>728482</v>
+        <v>728625</v>
       </c>
       <c r="R37" t="n">
-        <v>7172407</v>
+        <v>7172559</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4657,6 +4656,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4888,10 +4888,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117967004</v>
+        <v>117967239</v>
       </c>
       <c r="B40" t="n">
-        <v>90425</v>
+        <v>97857</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4900,30 +4900,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3242</v>
+        <v>221952</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4931,10 +4932,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>728521</v>
+        <v>728577</v>
       </c>
       <c r="R40" t="n">
-        <v>7172536</v>
+        <v>7172578</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5104,10 +5105,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117967010</v>
+        <v>117967004</v>
       </c>
       <c r="B42" t="n">
-        <v>56491</v>
+        <v>90425</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5120,31 +5121,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>3242</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5196,6 +5192,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5214,10 +5211,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117967239</v>
+        <v>117967010</v>
       </c>
       <c r="B43" t="n">
-        <v>97857</v>
+        <v>56491</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5226,31 +5223,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5258,10 +5259,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>728577</v>
+        <v>728521</v>
       </c>
       <c r="R43" t="n">
-        <v>7172578</v>
+        <v>7172536</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5302,7 +5303,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -8017,10 +8017,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117967291</v>
+        <v>117966930</v>
       </c>
       <c r="B69" t="n">
-        <v>97740</v>
+        <v>57287</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8029,31 +8029,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8061,10 +8065,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>728528</v>
+        <v>728532</v>
       </c>
       <c r="R69" t="n">
-        <v>7172601</v>
+        <v>7172473</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8099,13 +8103,17 @@
           <t>2024-06-21</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8124,10 +8132,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117966930</v>
+        <v>117967291</v>
       </c>
       <c r="B70" t="n">
-        <v>57287</v>
+        <v>97740</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8136,35 +8144,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8172,10 +8176,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>728532</v>
+        <v>728528</v>
       </c>
       <c r="R70" t="n">
-        <v>7172473</v>
+        <v>7172601</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8210,17 +8214,13 @@
           <t>2024-06-21</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8453,10 +8453,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117967162</v>
+        <v>117966856</v>
       </c>
       <c r="B73" t="n">
-        <v>57287</v>
+        <v>97836</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8465,35 +8465,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8501,10 +8497,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>728617</v>
+        <v>728516</v>
       </c>
       <c r="R73" t="n">
-        <v>7172533</v>
+        <v>7172454</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8545,6 +8541,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8563,7 +8560,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117966856</v>
+        <v>117966534</v>
       </c>
       <c r="B74" t="n">
         <v>97836</v>
@@ -8607,10 +8604,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>728516</v>
+        <v>728455</v>
       </c>
       <c r="R74" t="n">
-        <v>7172454</v>
+        <v>7172410</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8670,10 +8667,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117966534</v>
+        <v>117967162</v>
       </c>
       <c r="B75" t="n">
-        <v>97836</v>
+        <v>57287</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8682,31 +8679,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8714,10 +8715,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>728455</v>
+        <v>728617</v>
       </c>
       <c r="R75" t="n">
-        <v>7172410</v>
+        <v>7172533</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8758,7 +8759,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44648-2020 artfynd.xlsx
+++ b/artfynd/A 44648-2020 artfynd.xlsx
@@ -3149,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117966860</v>
+        <v>117967033</v>
       </c>
       <c r="B24" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,31 +3161,34 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3193,10 +3196,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>728516</v>
+        <v>728561</v>
       </c>
       <c r="R24" t="n">
-        <v>7172454</v>
+        <v>7172558</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3256,10 +3259,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117967370</v>
+        <v>117967525</v>
       </c>
       <c r="B25" t="n">
-        <v>97857</v>
+        <v>57303</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3268,31 +3271,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3300,13 +3307,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>728488</v>
+        <v>728504</v>
       </c>
       <c r="R25" t="n">
-        <v>7172629</v>
+        <v>7172502</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3344,7 +3351,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3363,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117967216</v>
+        <v>117967329</v>
       </c>
       <c r="B26" t="n">
-        <v>78480</v>
+        <v>97857</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,30 +3381,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3406,10 +3413,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>728577</v>
+        <v>728519</v>
       </c>
       <c r="R26" t="n">
-        <v>7172578</v>
+        <v>7172616</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3469,7 +3476,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117966993</v>
+        <v>117967216</v>
       </c>
       <c r="B27" t="n">
         <v>78480</v>
@@ -3504,11 +3511,7 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3516,10 +3519,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>728536</v>
+        <v>728577</v>
       </c>
       <c r="R27" t="n">
-        <v>7172529</v>
+        <v>7172578</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3579,10 +3582,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117967525</v>
+        <v>117967056</v>
       </c>
       <c r="B28" t="n">
-        <v>57303</v>
+        <v>78480</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3595,29 +3598,28 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3627,13 +3629,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>728504</v>
+        <v>728557</v>
       </c>
       <c r="R28" t="n">
-        <v>7172502</v>
+        <v>7172490</v>
       </c>
       <c r="S28" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3671,6 +3673,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3689,10 +3692,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117967449</v>
+        <v>117967162</v>
       </c>
       <c r="B29" t="n">
-        <v>97836</v>
+        <v>57287</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3701,31 +3704,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3733,13 +3740,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>728474</v>
+        <v>728617</v>
       </c>
       <c r="R29" t="n">
-        <v>7172591</v>
+        <v>7172533</v>
       </c>
       <c r="S29" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3777,7 +3784,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3796,10 +3802,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117967317</v>
+        <v>117967348</v>
       </c>
       <c r="B30" t="n">
-        <v>57287</v>
+        <v>97857</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3808,35 +3814,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3844,10 +3846,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>728519</v>
+        <v>728504</v>
       </c>
       <c r="R30" t="n">
-        <v>7172616</v>
+        <v>7172627</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3888,6 +3890,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3906,10 +3909,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117967348</v>
+        <v>117967459</v>
       </c>
       <c r="B31" t="n">
-        <v>97857</v>
+        <v>97836</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3918,25 +3921,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3950,13 +3953,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>728504</v>
+        <v>728499</v>
       </c>
       <c r="R31" t="n">
-        <v>7172627</v>
+        <v>7172520</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4013,10 +4016,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117966939</v>
+        <v>117967370</v>
       </c>
       <c r="B32" t="n">
-        <v>78480</v>
+        <v>97857</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4025,34 +4028,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>728530</v>
+        <v>728488</v>
       </c>
       <c r="R32" t="n">
-        <v>7172496</v>
+        <v>7172629</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117967497</v>
+        <v>117967381</v>
       </c>
       <c r="B33" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4139,29 +4139,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4171,13 +4170,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>728493</v>
+        <v>728472</v>
       </c>
       <c r="R33" t="n">
-        <v>7172518</v>
+        <v>7172667</v>
       </c>
       <c r="S33" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4215,6 +4214,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4233,10 +4233,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117967072</v>
+        <v>117966939</v>
       </c>
       <c r="B34" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4249,29 +4249,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4281,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>728557</v>
+        <v>728530</v>
       </c>
       <c r="R34" t="n">
-        <v>7172490</v>
+        <v>7172496</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4319,17 +4318,13 @@
           <t>2024-06-21</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4348,10 +4343,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117966745</v>
+        <v>117967601</v>
       </c>
       <c r="B35" t="n">
-        <v>97753</v>
+        <v>91253</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4360,35 +4355,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>366</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4396,13 +4386,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>728469</v>
+        <v>728455</v>
       </c>
       <c r="R35" t="n">
-        <v>7172427</v>
+        <v>7172412</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4459,7 +4449,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117965822</v>
+        <v>117967072</v>
       </c>
       <c r="B36" t="n">
         <v>57287</v>
@@ -4507,10 +4497,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>728482</v>
+        <v>728557</v>
       </c>
       <c r="R36" t="n">
-        <v>7172407</v>
+        <v>7172490</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4543,6 +4533,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4569,10 +4564,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117967205</v>
+        <v>117966402</v>
       </c>
       <c r="B37" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4581,30 +4576,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4612,10 +4608,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>728625</v>
+        <v>728464</v>
       </c>
       <c r="R37" t="n">
-        <v>7172559</v>
+        <v>7172420</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4675,10 +4671,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117966402</v>
+        <v>117967291</v>
       </c>
       <c r="B38" t="n">
-        <v>97836</v>
+        <v>97740</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4687,25 +4683,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4719,10 +4715,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>728464</v>
+        <v>728528</v>
       </c>
       <c r="R38" t="n">
-        <v>7172420</v>
+        <v>7172601</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4782,10 +4778,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117965826</v>
+        <v>117967048</v>
       </c>
       <c r="B39" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4798,21 +4794,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4825,10 +4821,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>728470</v>
+        <v>728583</v>
       </c>
       <c r="R39" t="n">
-        <v>7172400</v>
+        <v>7172562</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4888,10 +4884,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117967239</v>
+        <v>117967248</v>
       </c>
       <c r="B40" t="n">
-        <v>97857</v>
+        <v>79561</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4900,31 +4896,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4932,10 +4927,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>728577</v>
+        <v>728541</v>
       </c>
       <c r="R40" t="n">
-        <v>7172578</v>
+        <v>7172599</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4995,10 +4990,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117967547</v>
+        <v>117967514</v>
       </c>
       <c r="B41" t="n">
-        <v>78480</v>
+        <v>90648</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5007,34 +5002,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5042,10 +5033,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>728501</v>
+        <v>728495</v>
       </c>
       <c r="R41" t="n">
-        <v>7172494</v>
+        <v>7172520</v>
       </c>
       <c r="S41" t="n">
         <v>100</v>
@@ -5211,10 +5202,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117967010</v>
+        <v>117967497</v>
       </c>
       <c r="B43" t="n">
-        <v>56491</v>
+        <v>57287</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5227,16 +5218,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5249,7 +5240,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5259,13 +5250,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>728521</v>
+        <v>728493</v>
       </c>
       <c r="R43" t="n">
-        <v>7172536</v>
+        <v>7172518</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5321,10 +5312,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117967381</v>
+        <v>117967344</v>
       </c>
       <c r="B44" t="n">
-        <v>78480</v>
+        <v>97753</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5333,34 +5324,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5368,10 +5356,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>728472</v>
+        <v>728504</v>
       </c>
       <c r="R44" t="n">
-        <v>7172667</v>
+        <v>7172627</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5431,10 +5419,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117966898</v>
+        <v>117967279</v>
       </c>
       <c r="B45" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5443,30 +5431,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5474,10 +5463,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>728525</v>
+        <v>728528</v>
       </c>
       <c r="R45" t="n">
-        <v>7172470</v>
+        <v>7172601</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5537,10 +5526,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117967601</v>
+        <v>117967449</v>
       </c>
       <c r="B46" t="n">
-        <v>91253</v>
+        <v>97836</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5549,30 +5538,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>366</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5580,10 +5570,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>728455</v>
+        <v>728474</v>
       </c>
       <c r="R46" t="n">
-        <v>7172412</v>
+        <v>7172591</v>
       </c>
       <c r="S46" t="n">
         <v>100</v>
@@ -5643,10 +5633,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117965803</v>
+        <v>117967222</v>
       </c>
       <c r="B47" t="n">
-        <v>89570</v>
+        <v>79590</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5655,25 +5645,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1962</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5686,10 +5676,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>728482</v>
+        <v>728577</v>
       </c>
       <c r="R47" t="n">
-        <v>7172389</v>
+        <v>7172578</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5749,10 +5739,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117967033</v>
+        <v>117966571</v>
       </c>
       <c r="B48" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5765,30 +5755,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5796,10 +5782,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>728561</v>
+        <v>728455</v>
       </c>
       <c r="R48" t="n">
-        <v>7172558</v>
+        <v>7172410</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5859,10 +5845,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117966571</v>
+        <v>117967415</v>
       </c>
       <c r="B49" t="n">
-        <v>79561</v>
+        <v>78480</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5875,21 +5861,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5898,14 +5884,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Aborrklinten, Vb</t>
+          <t>64,6012546, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>728455</v>
+        <v>728470</v>
       </c>
       <c r="R49" t="n">
-        <v>7172410</v>
+        <v>7172604</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5965,7 +5951,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117966801</v>
+        <v>117965791</v>
       </c>
       <c r="B50" t="n">
         <v>78480</v>
@@ -6000,11 +5986,7 @@
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6012,10 +5994,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>728492</v>
+        <v>728475</v>
       </c>
       <c r="R50" t="n">
-        <v>7172423</v>
+        <v>7172370</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6075,10 +6057,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117967018</v>
+        <v>117967366</v>
       </c>
       <c r="B51" t="n">
-        <v>57287</v>
+        <v>97753</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6087,35 +6069,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6123,10 +6101,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>728521</v>
+        <v>728488</v>
       </c>
       <c r="R51" t="n">
-        <v>7172536</v>
+        <v>7172629</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6167,6 +6145,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6185,10 +6164,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117967542</v>
+        <v>117965803</v>
       </c>
       <c r="B52" t="n">
-        <v>57287</v>
+        <v>89570</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6201,31 +6180,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6233,13 +6207,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>728501</v>
+        <v>728482</v>
       </c>
       <c r="R52" t="n">
-        <v>7172494</v>
+        <v>7172389</v>
       </c>
       <c r="S52" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6277,6 +6251,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6295,10 +6270,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117967248</v>
+        <v>117966856</v>
       </c>
       <c r="B53" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6307,30 +6282,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6338,10 +6314,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>728541</v>
+        <v>728516</v>
       </c>
       <c r="R53" t="n">
-        <v>7172599</v>
+        <v>7172454</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6401,10 +6377,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117966905</v>
+        <v>117966745</v>
       </c>
       <c r="B54" t="n">
-        <v>78480</v>
+        <v>97753</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6413,34 +6389,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6448,10 +6425,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>728532</v>
+        <v>728469</v>
       </c>
       <c r="R54" t="n">
-        <v>7172451</v>
+        <v>7172427</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6511,10 +6488,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117965780</v>
+        <v>117967205</v>
       </c>
       <c r="B55" t="n">
-        <v>90510</v>
+        <v>78480</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6523,25 +6500,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6550,14 +6527,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Abottklinten, Vb</t>
+          <t>Aborrklinten, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>728493</v>
+        <v>728625</v>
       </c>
       <c r="R55" t="n">
-        <v>7172351</v>
+        <v>7172559</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6617,10 +6594,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117967514</v>
+        <v>117966963</v>
       </c>
       <c r="B56" t="n">
-        <v>90648</v>
+        <v>57440</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6629,30 +6606,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1503</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6660,13 +6642,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>728495</v>
+        <v>728529</v>
       </c>
       <c r="R56" t="n">
-        <v>7172520</v>
+        <v>7172527</v>
       </c>
       <c r="S56" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6704,7 +6686,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6829,10 +6810,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117967048</v>
+        <v>117967547</v>
       </c>
       <c r="B58" t="n">
-        <v>79561</v>
+        <v>78480</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6845,26 +6826,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6872,13 +6857,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>728583</v>
+        <v>728501</v>
       </c>
       <c r="R58" t="n">
-        <v>7172562</v>
+        <v>7172494</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6935,7 +6920,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117966877</v>
+        <v>117967317</v>
       </c>
       <c r="B59" t="n">
         <v>57287</v>
@@ -6983,10 +6968,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>728517</v>
+        <v>728519</v>
       </c>
       <c r="R59" t="n">
-        <v>7172466</v>
+        <v>7172616</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7019,11 +7004,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-06-21</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7050,10 +7030,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117967279</v>
+        <v>117967542</v>
       </c>
       <c r="B60" t="n">
-        <v>97836</v>
+        <v>57287</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7062,31 +7042,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7094,13 +7078,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>728528</v>
+        <v>728501</v>
       </c>
       <c r="R60" t="n">
-        <v>7172601</v>
+        <v>7172494</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7138,7 +7122,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7157,10 +7140,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117967366</v>
+        <v>117965822</v>
       </c>
       <c r="B61" t="n">
-        <v>97753</v>
+        <v>57287</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7169,31 +7152,35 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7201,10 +7188,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>728488</v>
+        <v>728482</v>
       </c>
       <c r="R61" t="n">
-        <v>7172629</v>
+        <v>7172407</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7245,7 +7232,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7264,10 +7250,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117967047</v>
+        <v>117967239</v>
       </c>
       <c r="B62" t="n">
-        <v>97836</v>
+        <v>97857</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7276,25 +7262,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7308,10 +7294,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>728583</v>
+        <v>728577</v>
       </c>
       <c r="R62" t="n">
-        <v>7172562</v>
+        <v>7172578</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7371,10 +7357,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117966795</v>
+        <v>117966905</v>
       </c>
       <c r="B63" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7383,35 +7369,34 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7419,10 +7404,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>728469</v>
+        <v>728532</v>
       </c>
       <c r="R63" t="n">
-        <v>7172427</v>
+        <v>7172451</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7482,10 +7467,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117967329</v>
+        <v>117966877</v>
       </c>
       <c r="B64" t="n">
-        <v>97857</v>
+        <v>57287</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7494,31 +7479,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7526,10 +7515,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>728519</v>
+        <v>728517</v>
       </c>
       <c r="R64" t="n">
-        <v>7172616</v>
+        <v>7172466</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7564,13 +7553,17 @@
           <t>2024-06-21</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7589,10 +7582,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117967056</v>
+        <v>117967026</v>
       </c>
       <c r="B65" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7605,28 +7598,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7636,10 +7638,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>728557</v>
+        <v>728521</v>
       </c>
       <c r="R65" t="n">
-        <v>7172490</v>
+        <v>7172536</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7680,7 +7682,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7699,10 +7700,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117966220</v>
+        <v>117967047</v>
       </c>
       <c r="B66" t="n">
-        <v>90425</v>
+        <v>97836</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7711,30 +7712,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7742,10 +7744,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>728457</v>
+        <v>728583</v>
       </c>
       <c r="R66" t="n">
-        <v>7172379</v>
+        <v>7172562</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7805,10 +7807,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117967222</v>
+        <v>117967010</v>
       </c>
       <c r="B67" t="n">
-        <v>79590</v>
+        <v>56491</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7817,30 +7819,35 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7848,10 +7855,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>728577</v>
+        <v>728521</v>
       </c>
       <c r="R67" t="n">
-        <v>7172578</v>
+        <v>7172536</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7892,7 +7899,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7911,10 +7917,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117965791</v>
+        <v>117966534</v>
       </c>
       <c r="B68" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7923,30 +7929,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7954,10 +7961,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>728475</v>
+        <v>728455</v>
       </c>
       <c r="R68" t="n">
-        <v>7172370</v>
+        <v>7172410</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8017,10 +8024,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117966930</v>
+        <v>117966795</v>
       </c>
       <c r="B69" t="n">
-        <v>57287</v>
+        <v>97857</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8029,35 +8036,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8065,10 +8072,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>728532</v>
+        <v>728469</v>
       </c>
       <c r="R69" t="n">
-        <v>7172473</v>
+        <v>7172427</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8103,17 +8110,13 @@
           <t>2024-06-21</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8132,10 +8135,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117967291</v>
+        <v>117967403</v>
       </c>
       <c r="B70" t="n">
-        <v>97740</v>
+        <v>97857</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8148,21 +8151,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8176,10 +8179,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>728528</v>
+        <v>728462</v>
       </c>
       <c r="R70" t="n">
-        <v>7172601</v>
+        <v>7172627</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8239,10 +8242,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117967344</v>
+        <v>117966860</v>
       </c>
       <c r="B71" t="n">
-        <v>97753</v>
+        <v>97857</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8255,21 +8258,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8283,10 +8286,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>728504</v>
+        <v>728516</v>
       </c>
       <c r="R71" t="n">
-        <v>7172627</v>
+        <v>7172454</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8346,10 +8349,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117967403</v>
+        <v>117965826</v>
       </c>
       <c r="B72" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8358,31 +8361,30 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8390,10 +8392,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>728462</v>
+        <v>728470</v>
       </c>
       <c r="R72" t="n">
-        <v>7172627</v>
+        <v>7172400</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8453,10 +8455,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117966856</v>
+        <v>117966801</v>
       </c>
       <c r="B73" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8465,31 +8467,34 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8497,10 +8502,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>728516</v>
+        <v>728492</v>
       </c>
       <c r="R73" t="n">
-        <v>7172454</v>
+        <v>7172423</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8560,10 +8565,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117966534</v>
+        <v>117965780</v>
       </c>
       <c r="B74" t="n">
-        <v>97836</v>
+        <v>90510</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8572,42 +8577,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Aborrklinten, Vb</t>
+          <t>Abottklinten, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>728455</v>
+        <v>728493</v>
       </c>
       <c r="R74" t="n">
-        <v>7172410</v>
+        <v>7172351</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8667,10 +8671,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117967162</v>
+        <v>117966220</v>
       </c>
       <c r="B75" t="n">
-        <v>57287</v>
+        <v>90425</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8683,31 +8687,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>3242</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8715,10 +8714,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>728617</v>
+        <v>728457</v>
       </c>
       <c r="R75" t="n">
-        <v>7172533</v>
+        <v>7172379</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8759,6 +8758,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8777,10 +8777,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117967459</v>
+        <v>117966930</v>
       </c>
       <c r="B76" t="n">
-        <v>97836</v>
+        <v>57287</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8789,31 +8789,35 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8821,13 +8825,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>728499</v>
+        <v>728532</v>
       </c>
       <c r="R76" t="n">
-        <v>7172520</v>
+        <v>7172473</v>
       </c>
       <c r="S76" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8859,13 +8863,17 @@
           <t>2024-06-21</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8884,7 +8892,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117967415</v>
+        <v>117966898</v>
       </c>
       <c r="B77" t="n">
         <v>78480</v>
@@ -8923,14 +8931,14 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>64,6012546, Vb</t>
+          <t>Aborrklinten, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>728470</v>
+        <v>728525</v>
       </c>
       <c r="R77" t="n">
-        <v>7172604</v>
+        <v>7172470</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8990,10 +8998,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117966963</v>
+        <v>117966993</v>
       </c>
       <c r="B78" t="n">
-        <v>57440</v>
+        <v>78480</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9006,29 +9014,28 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -9038,10 +9045,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>728529</v>
+        <v>728536</v>
       </c>
       <c r="R78" t="n">
-        <v>7172527</v>
+        <v>7172529</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9082,6 +9089,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44648-2020 artfynd.xlsx
+++ b/artfynd/A 44648-2020 artfynd.xlsx
@@ -3149,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117967033</v>
+        <v>117967366</v>
       </c>
       <c r="B24" t="n">
-        <v>78480</v>
+        <v>97755</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,34 +3161,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3196,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>728561</v>
+        <v>728488</v>
       </c>
       <c r="R24" t="n">
-        <v>7172558</v>
+        <v>7172629</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3259,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117967525</v>
+        <v>117967329</v>
       </c>
       <c r="B25" t="n">
-        <v>57303</v>
+        <v>97859</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3271,35 +3268,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3307,13 +3300,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>728504</v>
+        <v>728519</v>
       </c>
       <c r="R25" t="n">
-        <v>7172502</v>
+        <v>7172616</v>
       </c>
       <c r="S25" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3351,6 +3344,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3369,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117967329</v>
+        <v>117967449</v>
       </c>
       <c r="B26" t="n">
-        <v>97857</v>
+        <v>97838</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3381,25 +3375,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3413,13 +3407,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>728519</v>
+        <v>728474</v>
       </c>
       <c r="R26" t="n">
-        <v>7172616</v>
+        <v>7172591</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3476,10 +3470,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117967216</v>
+        <v>117966801</v>
       </c>
       <c r="B27" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3511,7 +3505,11 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3519,10 +3517,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>728577</v>
+        <v>728492</v>
       </c>
       <c r="R27" t="n">
-        <v>7172578</v>
+        <v>7172423</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3582,10 +3580,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117967056</v>
+        <v>117967222</v>
       </c>
       <c r="B28" t="n">
-        <v>78480</v>
+        <v>79592</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3594,34 +3592,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3629,10 +3623,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>728557</v>
+        <v>728577</v>
       </c>
       <c r="R28" t="n">
-        <v>7172490</v>
+        <v>7172578</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3692,10 +3686,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117967162</v>
+        <v>117967047</v>
       </c>
       <c r="B29" t="n">
-        <v>57287</v>
+        <v>97838</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3704,35 +3698,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3740,10 +3730,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>728617</v>
+        <v>728583</v>
       </c>
       <c r="R29" t="n">
-        <v>7172533</v>
+        <v>7172562</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3784,6 +3774,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3802,10 +3793,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117967348</v>
+        <v>117967403</v>
       </c>
       <c r="B30" t="n">
-        <v>97857</v>
+        <v>97859</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3846,7 +3837,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>728504</v>
+        <v>728462</v>
       </c>
       <c r="R30" t="n">
         <v>7172627</v>
@@ -3909,10 +3900,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117967459</v>
+        <v>117967370</v>
       </c>
       <c r="B31" t="n">
-        <v>97836</v>
+        <v>97859</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3921,25 +3912,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3953,13 +3944,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>728499</v>
+        <v>728488</v>
       </c>
       <c r="R31" t="n">
-        <v>7172520</v>
+        <v>7172629</v>
       </c>
       <c r="S31" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4016,10 +4007,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117967370</v>
+        <v>117967018</v>
       </c>
       <c r="B32" t="n">
-        <v>97857</v>
+        <v>57288</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4028,31 +4019,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4060,10 +4055,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>728488</v>
+        <v>728521</v>
       </c>
       <c r="R32" t="n">
-        <v>7172629</v>
+        <v>7172536</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4104,7 +4099,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4123,10 +4117,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117967381</v>
+        <v>117967601</v>
       </c>
       <c r="B33" t="n">
-        <v>78480</v>
+        <v>91255</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4139,30 +4133,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>366</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4170,13 +4160,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>728472</v>
+        <v>728455</v>
       </c>
       <c r="R33" t="n">
-        <v>7172667</v>
+        <v>7172412</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4233,10 +4223,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117966939</v>
+        <v>117967317</v>
       </c>
       <c r="B34" t="n">
-        <v>78480</v>
+        <v>57288</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4249,28 +4239,29 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4280,10 +4271,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>728530</v>
+        <v>728519</v>
       </c>
       <c r="R34" t="n">
-        <v>7172496</v>
+        <v>7172616</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4324,7 +4315,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4343,10 +4333,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117967601</v>
+        <v>117967048</v>
       </c>
       <c r="B35" t="n">
-        <v>91253</v>
+        <v>79563</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4359,21 +4349,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>366</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4386,13 +4376,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>728455</v>
+        <v>728583</v>
       </c>
       <c r="R35" t="n">
-        <v>7172412</v>
+        <v>7172562</v>
       </c>
       <c r="S35" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4449,10 +4439,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117967072</v>
+        <v>117965826</v>
       </c>
       <c r="B36" t="n">
-        <v>57287</v>
+        <v>78482</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4465,31 +4455,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4497,10 +4482,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>728557</v>
+        <v>728470</v>
       </c>
       <c r="R36" t="n">
-        <v>7172490</v>
+        <v>7172400</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4535,17 +4520,13 @@
           <t>2024-06-21</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4564,10 +4545,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117966402</v>
+        <v>117966220</v>
       </c>
       <c r="B37" t="n">
-        <v>97836</v>
+        <v>90427</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4576,31 +4557,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4608,10 +4588,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>728464</v>
+        <v>728457</v>
       </c>
       <c r="R37" t="n">
-        <v>7172420</v>
+        <v>7172379</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4671,10 +4651,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117967291</v>
+        <v>117966856</v>
       </c>
       <c r="B38" t="n">
-        <v>97740</v>
+        <v>97838</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4683,25 +4663,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4715,10 +4695,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>728528</v>
+        <v>728516</v>
       </c>
       <c r="R38" t="n">
-        <v>7172601</v>
+        <v>7172454</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4778,10 +4758,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117967048</v>
+        <v>117967239</v>
       </c>
       <c r="B39" t="n">
-        <v>79561</v>
+        <v>97859</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4790,30 +4770,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4821,10 +4802,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>728583</v>
+        <v>728577</v>
       </c>
       <c r="R39" t="n">
-        <v>7172562</v>
+        <v>7172578</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4884,10 +4865,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117967248</v>
+        <v>117967004</v>
       </c>
       <c r="B40" t="n">
-        <v>79561</v>
+        <v>90427</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4900,21 +4881,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>3242</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4927,10 +4908,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>728541</v>
+        <v>728521</v>
       </c>
       <c r="R40" t="n">
-        <v>7172599</v>
+        <v>7172536</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4990,10 +4971,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117967514</v>
+        <v>117965780</v>
       </c>
       <c r="B41" t="n">
-        <v>90648</v>
+        <v>90512</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5002,25 +4983,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1503</v>
+        <v>1205</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5029,17 +5010,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Aborrklinten, Vb</t>
+          <t>Abottklinten, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>728495</v>
+        <v>728493</v>
       </c>
       <c r="R41" t="n">
-        <v>7172520</v>
+        <v>7172351</v>
       </c>
       <c r="S41" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5096,10 +5077,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117967004</v>
+        <v>117967056</v>
       </c>
       <c r="B42" t="n">
-        <v>90425</v>
+        <v>78482</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5112,26 +5093,30 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5139,10 +5124,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>728521</v>
+        <v>728557</v>
       </c>
       <c r="R42" t="n">
-        <v>7172536</v>
+        <v>7172490</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5202,10 +5187,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117967497</v>
+        <v>117965791</v>
       </c>
       <c r="B43" t="n">
-        <v>57287</v>
+        <v>78482</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5218,31 +5203,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5250,13 +5230,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>728493</v>
+        <v>728475</v>
       </c>
       <c r="R43" t="n">
-        <v>7172518</v>
+        <v>7172370</v>
       </c>
       <c r="S43" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5294,6 +5274,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5312,10 +5293,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117967344</v>
+        <v>117966930</v>
       </c>
       <c r="B44" t="n">
-        <v>97753</v>
+        <v>57288</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5324,31 +5305,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5356,10 +5341,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>728504</v>
+        <v>728532</v>
       </c>
       <c r="R44" t="n">
-        <v>7172627</v>
+        <v>7172473</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5394,13 +5379,17 @@
           <t>2024-06-21</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5419,10 +5408,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117967279</v>
+        <v>117965822</v>
       </c>
       <c r="B45" t="n">
-        <v>97836</v>
+        <v>57288</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5431,31 +5420,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5463,10 +5456,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>728528</v>
+        <v>728482</v>
       </c>
       <c r="R45" t="n">
-        <v>7172601</v>
+        <v>7172407</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5507,7 +5500,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5526,10 +5518,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117967449</v>
+        <v>117967162</v>
       </c>
       <c r="B46" t="n">
-        <v>97836</v>
+        <v>57288</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5538,31 +5530,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5570,13 +5566,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>728474</v>
+        <v>728617</v>
       </c>
       <c r="R46" t="n">
-        <v>7172591</v>
+        <v>7172533</v>
       </c>
       <c r="S46" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5614,7 +5610,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5633,10 +5628,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117967222</v>
+        <v>117966571</v>
       </c>
       <c r="B47" t="n">
-        <v>79590</v>
+        <v>79563</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5645,25 +5640,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5676,10 +5671,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>728577</v>
+        <v>728455</v>
       </c>
       <c r="R47" t="n">
-        <v>7172578</v>
+        <v>7172410</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5739,10 +5734,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117966571</v>
+        <v>117967279</v>
       </c>
       <c r="B48" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5751,30 +5746,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5782,10 +5778,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>728455</v>
+        <v>728528</v>
       </c>
       <c r="R48" t="n">
-        <v>7172410</v>
+        <v>7172601</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5845,10 +5841,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117967415</v>
+        <v>117967525</v>
       </c>
       <c r="B49" t="n">
-        <v>78480</v>
+        <v>57304</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5861,40 +5857,45 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>64,6012546, Vb</t>
+          <t>Aborrklinten, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>728470</v>
+        <v>728504</v>
       </c>
       <c r="R49" t="n">
-        <v>7172604</v>
+        <v>7172502</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5932,7 +5933,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5951,10 +5951,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117965791</v>
+        <v>117967033</v>
       </c>
       <c r="B50" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5986,7 +5986,11 @@
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5994,10 +5998,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>728475</v>
+        <v>728561</v>
       </c>
       <c r="R50" t="n">
-        <v>7172370</v>
+        <v>7172558</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6057,10 +6061,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117967366</v>
+        <v>117966905</v>
       </c>
       <c r="B51" t="n">
-        <v>97753</v>
+        <v>78482</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6069,31 +6073,34 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6101,10 +6108,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>728488</v>
+        <v>728532</v>
       </c>
       <c r="R51" t="n">
-        <v>7172629</v>
+        <v>7172451</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6164,10 +6171,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117965803</v>
+        <v>117967216</v>
       </c>
       <c r="B52" t="n">
-        <v>89570</v>
+        <v>78482</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6180,21 +6187,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6207,10 +6214,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>728482</v>
+        <v>728577</v>
       </c>
       <c r="R52" t="n">
-        <v>7172389</v>
+        <v>7172578</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6270,10 +6277,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117966856</v>
+        <v>117967381</v>
       </c>
       <c r="B53" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6282,31 +6289,34 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6314,10 +6324,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>728516</v>
+        <v>728472</v>
       </c>
       <c r="R53" t="n">
-        <v>7172454</v>
+        <v>7172667</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6377,10 +6387,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117966745</v>
+        <v>117966997</v>
       </c>
       <c r="B54" t="n">
-        <v>97753</v>
+        <v>90466</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6393,31 +6403,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6425,10 +6430,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>728469</v>
+        <v>728521</v>
       </c>
       <c r="R54" t="n">
-        <v>7172427</v>
+        <v>7172536</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6488,10 +6493,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117967205</v>
+        <v>117967547</v>
       </c>
       <c r="B55" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6523,7 +6528,11 @@
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6531,13 +6540,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>728625</v>
+        <v>728501</v>
       </c>
       <c r="R55" t="n">
-        <v>7172559</v>
+        <v>7172494</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6594,10 +6603,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117966963</v>
+        <v>117966860</v>
       </c>
       <c r="B56" t="n">
-        <v>57440</v>
+        <v>97859</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6606,35 +6615,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6642,10 +6647,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>728529</v>
+        <v>728516</v>
       </c>
       <c r="R56" t="n">
-        <v>7172527</v>
+        <v>7172454</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6686,6 +6691,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6704,10 +6710,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117966997</v>
+        <v>117966402</v>
       </c>
       <c r="B57" t="n">
-        <v>90464</v>
+        <v>97838</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6716,30 +6722,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6747,10 +6754,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>728521</v>
+        <v>728464</v>
       </c>
       <c r="R57" t="n">
-        <v>7172536</v>
+        <v>7172420</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6810,10 +6817,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117967547</v>
+        <v>117965803</v>
       </c>
       <c r="B58" t="n">
-        <v>78480</v>
+        <v>89572</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6826,30 +6833,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6857,13 +6860,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>728501</v>
+        <v>728482</v>
       </c>
       <c r="R58" t="n">
-        <v>7172494</v>
+        <v>7172389</v>
       </c>
       <c r="S58" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6920,10 +6923,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117967317</v>
+        <v>117966898</v>
       </c>
       <c r="B59" t="n">
-        <v>57287</v>
+        <v>78482</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6936,31 +6939,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6968,10 +6966,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>728519</v>
+        <v>728525</v>
       </c>
       <c r="R59" t="n">
-        <v>7172616</v>
+        <v>7172470</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7012,6 +7010,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7030,10 +7029,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117967542</v>
+        <v>117966963</v>
       </c>
       <c r="B60" t="n">
-        <v>57287</v>
+        <v>57441</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7046,21 +7045,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7068,7 +7067,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7078,13 +7077,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>728501</v>
+        <v>728529</v>
       </c>
       <c r="R60" t="n">
-        <v>7172494</v>
+        <v>7172527</v>
       </c>
       <c r="S60" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7140,10 +7139,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117965822</v>
+        <v>117967344</v>
       </c>
       <c r="B61" t="n">
-        <v>57287</v>
+        <v>97755</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7152,35 +7151,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7188,10 +7183,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>728482</v>
+        <v>728504</v>
       </c>
       <c r="R61" t="n">
-        <v>7172407</v>
+        <v>7172627</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7232,6 +7227,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7250,10 +7246,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117967239</v>
+        <v>117966939</v>
       </c>
       <c r="B62" t="n">
-        <v>97857</v>
+        <v>78482</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7262,31 +7258,34 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7294,10 +7293,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>728577</v>
+        <v>728530</v>
       </c>
       <c r="R62" t="n">
-        <v>7172578</v>
+        <v>7172496</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7357,10 +7356,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117966905</v>
+        <v>117967415</v>
       </c>
       <c r="B63" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7392,22 +7391,18 @@
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Aborrklinten, Vb</t>
+          <t>64,6012546, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>728532</v>
+        <v>728470</v>
       </c>
       <c r="R63" t="n">
-        <v>7172451</v>
+        <v>7172604</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7467,10 +7462,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117966877</v>
+        <v>117966795</v>
       </c>
       <c r="B64" t="n">
-        <v>57287</v>
+        <v>97859</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7479,35 +7474,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7515,10 +7510,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>728517</v>
+        <v>728469</v>
       </c>
       <c r="R64" t="n">
-        <v>7172466</v>
+        <v>7172427</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7553,17 +7548,13 @@
           <t>2024-06-21</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7582,10 +7573,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117967026</v>
+        <v>117966745</v>
       </c>
       <c r="B65" t="n">
-        <v>57287</v>
+        <v>97755</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7594,43 +7585,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>besöker bebott bo</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7638,10 +7621,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>728521</v>
+        <v>728469</v>
       </c>
       <c r="R65" t="n">
-        <v>7172536</v>
+        <v>7172427</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7682,6 +7665,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7700,10 +7684,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117967047</v>
+        <v>117967459</v>
       </c>
       <c r="B66" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7744,13 +7728,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>728583</v>
+        <v>728499</v>
       </c>
       <c r="R66" t="n">
-        <v>7172562</v>
+        <v>7172520</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7807,10 +7791,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117967010</v>
+        <v>117967072</v>
       </c>
       <c r="B67" t="n">
-        <v>56491</v>
+        <v>57288</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7823,16 +7807,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7845,7 +7829,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7855,10 +7839,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>728521</v>
+        <v>728557</v>
       </c>
       <c r="R67" t="n">
-        <v>7172536</v>
+        <v>7172490</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7891,6 +7875,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7917,10 +7906,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117966534</v>
+        <v>117966993</v>
       </c>
       <c r="B68" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7929,31 +7918,34 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7961,10 +7953,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>728455</v>
+        <v>728536</v>
       </c>
       <c r="R68" t="n">
-        <v>7172410</v>
+        <v>7172529</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8024,10 +8016,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117966795</v>
+        <v>117967497</v>
       </c>
       <c r="B69" t="n">
-        <v>97857</v>
+        <v>57288</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8036,35 +8028,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8072,13 +8064,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>728469</v>
+        <v>728493</v>
       </c>
       <c r="R69" t="n">
-        <v>7172427</v>
+        <v>7172518</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8116,7 +8108,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8135,10 +8126,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117967403</v>
+        <v>117966877</v>
       </c>
       <c r="B70" t="n">
-        <v>97857</v>
+        <v>57288</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8147,31 +8138,35 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8179,10 +8174,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>728462</v>
+        <v>728517</v>
       </c>
       <c r="R70" t="n">
-        <v>7172627</v>
+        <v>7172466</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8217,13 +8212,17 @@
           <t>2024-06-21</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8242,10 +8241,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117966860</v>
+        <v>117967348</v>
       </c>
       <c r="B71" t="n">
-        <v>97857</v>
+        <v>97859</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8286,10 +8285,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>728516</v>
+        <v>728504</v>
       </c>
       <c r="R71" t="n">
-        <v>7172454</v>
+        <v>7172627</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8349,10 +8348,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117965826</v>
+        <v>117967514</v>
       </c>
       <c r="B72" t="n">
-        <v>78480</v>
+        <v>90650</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8361,25 +8360,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8392,13 +8391,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>728470</v>
+        <v>728495</v>
       </c>
       <c r="R72" t="n">
-        <v>7172400</v>
+        <v>7172520</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8455,10 +8454,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117966801</v>
+        <v>117967291</v>
       </c>
       <c r="B73" t="n">
-        <v>78480</v>
+        <v>97742</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8467,34 +8466,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8502,10 +8498,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>728492</v>
+        <v>728528</v>
       </c>
       <c r="R73" t="n">
-        <v>7172423</v>
+        <v>7172601</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8565,10 +8561,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117965780</v>
+        <v>117967248</v>
       </c>
       <c r="B74" t="n">
-        <v>90510</v>
+        <v>79563</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8577,25 +8573,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8604,14 +8600,14 @@
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Abottklinten, Vb</t>
+          <t>Aborrklinten, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>728493</v>
+        <v>728541</v>
       </c>
       <c r="R74" t="n">
-        <v>7172351</v>
+        <v>7172599</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8671,10 +8667,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117966220</v>
+        <v>117967205</v>
       </c>
       <c r="B75" t="n">
-        <v>90425</v>
+        <v>78482</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8687,21 +8683,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8714,10 +8710,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>728457</v>
+        <v>728625</v>
       </c>
       <c r="R75" t="n">
-        <v>7172379</v>
+        <v>7172559</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8777,10 +8773,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117966930</v>
+        <v>117967542</v>
       </c>
       <c r="B76" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8815,7 +8811,7 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8825,13 +8821,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>728532</v>
+        <v>728501</v>
       </c>
       <c r="R76" t="n">
-        <v>7172473</v>
+        <v>7172494</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8861,11 +8857,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-06-21</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8892,10 +8883,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117966898</v>
+        <v>117967010</v>
       </c>
       <c r="B77" t="n">
-        <v>78480</v>
+        <v>56492</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8908,26 +8899,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8935,10 +8931,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>728525</v>
+        <v>728521</v>
       </c>
       <c r="R77" t="n">
-        <v>7172470</v>
+        <v>7172536</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8979,7 +8975,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8998,10 +8993,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117966993</v>
+        <v>117966534</v>
       </c>
       <c r="B78" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9010,34 +9005,31 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9045,10 +9037,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>728536</v>
+        <v>728455</v>
       </c>
       <c r="R78" t="n">
-        <v>7172529</v>
+        <v>7172410</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 44648-2020 artfynd.xlsx
+++ b/artfynd/A 44648-2020 artfynd.xlsx
@@ -4651,10 +4651,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117966856</v>
+        <v>117967239</v>
       </c>
       <c r="B38" t="n">
-        <v>97838</v>
+        <v>97859</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4663,25 +4663,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>728516</v>
+        <v>728577</v>
       </c>
       <c r="R38" t="n">
-        <v>7172454</v>
+        <v>7172578</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4758,10 +4758,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117967239</v>
+        <v>117966856</v>
       </c>
       <c r="B39" t="n">
-        <v>97859</v>
+        <v>97838</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4770,25 +4770,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>728577</v>
+        <v>728516</v>
       </c>
       <c r="R39" t="n">
-        <v>7172578</v>
+        <v>7172454</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -7684,10 +7684,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117967459</v>
+        <v>117967072</v>
       </c>
       <c r="B66" t="n">
-        <v>97838</v>
+        <v>57288</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7696,31 +7696,35 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7728,13 +7732,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>728499</v>
+        <v>728557</v>
       </c>
       <c r="R66" t="n">
-        <v>7172520</v>
+        <v>7172490</v>
       </c>
       <c r="S66" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7766,13 +7770,17 @@
           <t>2024-06-21</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7791,10 +7799,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117967072</v>
+        <v>117966993</v>
       </c>
       <c r="B67" t="n">
-        <v>57288</v>
+        <v>78482</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7807,29 +7815,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7839,10 +7846,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>728557</v>
+        <v>728536</v>
       </c>
       <c r="R67" t="n">
-        <v>7172490</v>
+        <v>7172529</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7877,17 +7884,13 @@
           <t>2024-06-21</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7906,10 +7909,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117966993</v>
+        <v>117967459</v>
       </c>
       <c r="B68" t="n">
-        <v>78482</v>
+        <v>97838</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7918,34 +7921,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7953,13 +7953,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>728536</v>
+        <v>728499</v>
       </c>
       <c r="R68" t="n">
-        <v>7172529</v>
+        <v>7172520</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117967497</v>
+        <v>117967291</v>
       </c>
       <c r="B69" t="n">
-        <v>57288</v>
+        <v>97742</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8028,35 +8028,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8064,13 +8060,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>728493</v>
+        <v>728528</v>
       </c>
       <c r="R69" t="n">
-        <v>7172518</v>
+        <v>7172601</v>
       </c>
       <c r="S69" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8108,6 +8104,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8126,10 +8123,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117966877</v>
+        <v>117967348</v>
       </c>
       <c r="B70" t="n">
-        <v>57288</v>
+        <v>97859</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8138,35 +8135,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8174,10 +8167,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>728517</v>
+        <v>728504</v>
       </c>
       <c r="R70" t="n">
-        <v>7172466</v>
+        <v>7172627</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8212,17 +8205,13 @@
           <t>2024-06-21</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8241,10 +8230,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117967348</v>
+        <v>117967497</v>
       </c>
       <c r="B71" t="n">
-        <v>97859</v>
+        <v>57288</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8253,31 +8242,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8285,13 +8278,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>728504</v>
+        <v>728493</v>
       </c>
       <c r="R71" t="n">
-        <v>7172627</v>
+        <v>7172518</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8329,7 +8322,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8348,10 +8340,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117967514</v>
+        <v>117966877</v>
       </c>
       <c r="B72" t="n">
-        <v>90650</v>
+        <v>57288</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8360,30 +8352,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8391,13 +8388,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>728495</v>
+        <v>728517</v>
       </c>
       <c r="R72" t="n">
-        <v>7172520</v>
+        <v>7172466</v>
       </c>
       <c r="S72" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8429,13 +8426,17 @@
           <t>2024-06-21</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8454,10 +8455,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117967291</v>
+        <v>117967514</v>
       </c>
       <c r="B73" t="n">
-        <v>97742</v>
+        <v>90650</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8466,31 +8467,30 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220093</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8498,13 +8498,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>728528</v>
+        <v>728495</v>
       </c>
       <c r="R73" t="n">
-        <v>7172601</v>
+        <v>7172520</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>

--- a/artfynd/A 44648-2020 artfynd.xlsx
+++ b/artfynd/A 44648-2020 artfynd.xlsx
@@ -9108,7 +9108,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119796714</v>
+        <v>119796716</v>
       </c>
       <c r="B79" t="n">
         <v>97907</v>
@@ -9152,10 +9152,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>728468</v>
+        <v>728446</v>
       </c>
       <c r="R79" t="n">
-        <v>7172390</v>
+        <v>7172530</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9219,7 +9219,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119796718</v>
+        <v>119796720</v>
       </c>
       <c r="B80" t="n">
         <v>97907</v>
@@ -9263,10 +9263,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>728471</v>
+        <v>728494</v>
       </c>
       <c r="R80" t="n">
-        <v>7172510</v>
+        <v>7172550</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9330,7 +9330,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119796717</v>
+        <v>119796713</v>
       </c>
       <c r="B81" t="n">
         <v>97907</v>
@@ -9374,10 +9374,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>728451</v>
+        <v>728479</v>
       </c>
       <c r="R81" t="n">
-        <v>7172520</v>
+        <v>7172390</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9441,7 +9441,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119796715</v>
+        <v>119796721</v>
       </c>
       <c r="B82" t="n">
         <v>97907</v>
@@ -9485,10 +9485,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>728459</v>
+        <v>728587</v>
       </c>
       <c r="R82" t="n">
-        <v>7172400</v>
+        <v>7172540</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9552,7 +9552,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119796716</v>
+        <v>119796718</v>
       </c>
       <c r="B83" t="n">
         <v>97907</v>
@@ -9596,10 +9596,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>728446</v>
+        <v>728471</v>
       </c>
       <c r="R83" t="n">
-        <v>7172530</v>
+        <v>7172510</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9663,7 +9663,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119796713</v>
+        <v>119796717</v>
       </c>
       <c r="B84" t="n">
         <v>97907</v>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>728479</v>
+        <v>728451</v>
       </c>
       <c r="R84" t="n">
-        <v>7172390</v>
+        <v>7172520</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9774,7 +9774,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119796720</v>
+        <v>119796715</v>
       </c>
       <c r="B85" t="n">
         <v>97907</v>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>728494</v>
+        <v>728459</v>
       </c>
       <c r="R85" t="n">
-        <v>7172550</v>
+        <v>7172400</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9885,7 +9885,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119796719</v>
+        <v>119796714</v>
       </c>
       <c r="B86" t="n">
         <v>97907</v>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>728496</v>
+        <v>728468</v>
       </c>
       <c r="R86" t="n">
-        <v>7172530</v>
+        <v>7172390</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9996,7 +9996,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119796721</v>
+        <v>119796719</v>
       </c>
       <c r="B87" t="n">
         <v>97907</v>
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>728587</v>
+        <v>728496</v>
       </c>
       <c r="R87" t="n">
-        <v>7172540</v>
+        <v>7172530</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 44648-2020 artfynd.xlsx
+++ b/artfynd/A 44648-2020 artfynd.xlsx
@@ -9219,7 +9219,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119796720</v>
+        <v>119796713</v>
       </c>
       <c r="B80" t="n">
         <v>97907</v>
@@ -9263,10 +9263,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>728494</v>
+        <v>728479</v>
       </c>
       <c r="R80" t="n">
-        <v>7172550</v>
+        <v>7172390</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9330,7 +9330,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119796713</v>
+        <v>119796720</v>
       </c>
       <c r="B81" t="n">
         <v>97907</v>
@@ -9374,10 +9374,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>728479</v>
+        <v>728494</v>
       </c>
       <c r="R81" t="n">
-        <v>7172390</v>
+        <v>7172550</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9441,7 +9441,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119796721</v>
+        <v>119796715</v>
       </c>
       <c r="B82" t="n">
         <v>97907</v>
@@ -9485,10 +9485,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>728587</v>
+        <v>728459</v>
       </c>
       <c r="R82" t="n">
-        <v>7172540</v>
+        <v>7172400</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9663,7 +9663,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119796717</v>
+        <v>119796714</v>
       </c>
       <c r="B84" t="n">
         <v>97907</v>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>728451</v>
+        <v>728468</v>
       </c>
       <c r="R84" t="n">
-        <v>7172520</v>
+        <v>7172390</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9774,7 +9774,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119796715</v>
+        <v>119796721</v>
       </c>
       <c r="B85" t="n">
         <v>97907</v>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>728459</v>
+        <v>728587</v>
       </c>
       <c r="R85" t="n">
-        <v>7172400</v>
+        <v>7172540</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9885,7 +9885,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119796714</v>
+        <v>119796717</v>
       </c>
       <c r="B86" t="n">
         <v>97907</v>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>728468</v>
+        <v>728451</v>
       </c>
       <c r="R86" t="n">
-        <v>7172390</v>
+        <v>7172520</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 44648-2020 artfynd.xlsx
+++ b/artfynd/A 44648-2020 artfynd.xlsx
@@ -9108,7 +9108,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119796716</v>
+        <v>119796715</v>
       </c>
       <c r="B79" t="n">
         <v>97907</v>
@@ -9152,10 +9152,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>728446</v>
+        <v>728459</v>
       </c>
       <c r="R79" t="n">
-        <v>7172530</v>
+        <v>7172400</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9219,7 +9219,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119796713</v>
+        <v>119796717</v>
       </c>
       <c r="B80" t="n">
         <v>97907</v>
@@ -9263,10 +9263,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>728479</v>
+        <v>728451</v>
       </c>
       <c r="R80" t="n">
-        <v>7172390</v>
+        <v>7172520</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9330,7 +9330,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119796720</v>
+        <v>119796721</v>
       </c>
       <c r="B81" t="n">
         <v>97907</v>
@@ -9374,10 +9374,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>728494</v>
+        <v>728587</v>
       </c>
       <c r="R81" t="n">
-        <v>7172550</v>
+        <v>7172540</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9441,7 +9441,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119796715</v>
+        <v>119796714</v>
       </c>
       <c r="B82" t="n">
         <v>97907</v>
@@ -9485,10 +9485,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>728459</v>
+        <v>728468</v>
       </c>
       <c r="R82" t="n">
-        <v>7172400</v>
+        <v>7172390</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9552,7 +9552,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119796718</v>
+        <v>119796713</v>
       </c>
       <c r="B83" t="n">
         <v>97907</v>
@@ -9596,10 +9596,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>728471</v>
+        <v>728479</v>
       </c>
       <c r="R83" t="n">
-        <v>7172510</v>
+        <v>7172390</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9663,7 +9663,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119796714</v>
+        <v>119796716</v>
       </c>
       <c r="B84" t="n">
         <v>97907</v>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>728468</v>
+        <v>728446</v>
       </c>
       <c r="R84" t="n">
-        <v>7172390</v>
+        <v>7172530</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9774,7 +9774,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119796721</v>
+        <v>119796719</v>
       </c>
       <c r="B85" t="n">
         <v>97907</v>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>728587</v>
+        <v>728496</v>
       </c>
       <c r="R85" t="n">
-        <v>7172540</v>
+        <v>7172530</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9885,7 +9885,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119796717</v>
+        <v>119796718</v>
       </c>
       <c r="B86" t="n">
         <v>97907</v>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>728451</v>
+        <v>728471</v>
       </c>
       <c r="R86" t="n">
-        <v>7172520</v>
+        <v>7172510</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9996,7 +9996,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119796719</v>
+        <v>119796720</v>
       </c>
       <c r="B87" t="n">
         <v>97907</v>
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>728496</v>
+        <v>728494</v>
       </c>
       <c r="R87" t="n">
-        <v>7172530</v>
+        <v>7172550</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 44648-2020 artfynd.xlsx
+++ b/artfynd/A 44648-2020 artfynd.xlsx
@@ -9108,10 +9108,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119796715</v>
+        <v>119796718</v>
       </c>
       <c r="B79" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9152,10 +9152,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>728459</v>
+        <v>728471</v>
       </c>
       <c r="R79" t="n">
-        <v>7172400</v>
+        <v>7172510</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9222,7 +9222,7 @@
         <v>119796717</v>
       </c>
       <c r="B80" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9330,10 +9330,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119796721</v>
+        <v>119796713</v>
       </c>
       <c r="B81" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9374,10 +9374,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>728587</v>
+        <v>728479</v>
       </c>
       <c r="R81" t="n">
-        <v>7172540</v>
+        <v>7172390</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9441,10 +9441,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119796714</v>
+        <v>119796720</v>
       </c>
       <c r="B82" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9485,10 +9485,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>728468</v>
+        <v>728494</v>
       </c>
       <c r="R82" t="n">
-        <v>7172390</v>
+        <v>7172550</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9552,10 +9552,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119796713</v>
+        <v>119796715</v>
       </c>
       <c r="B83" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9596,10 +9596,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>728479</v>
+        <v>728459</v>
       </c>
       <c r="R83" t="n">
-        <v>7172390</v>
+        <v>7172400</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9666,7 +9666,7 @@
         <v>119796716</v>
       </c>
       <c r="B84" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9774,10 +9774,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119796719</v>
+        <v>119796714</v>
       </c>
       <c r="B85" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>728496</v>
+        <v>728468</v>
       </c>
       <c r="R85" t="n">
-        <v>7172530</v>
+        <v>7172390</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9885,10 +9885,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119796718</v>
+        <v>119796721</v>
       </c>
       <c r="B86" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>728471</v>
+        <v>728587</v>
       </c>
       <c r="R86" t="n">
-        <v>7172510</v>
+        <v>7172540</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9996,10 +9996,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119796720</v>
+        <v>119796719</v>
       </c>
       <c r="B87" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>728494</v>
+        <v>728496</v>
       </c>
       <c r="R87" t="n">
-        <v>7172550</v>
+        <v>7172530</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 44648-2020 artfynd.xlsx
+++ b/artfynd/A 44648-2020 artfynd.xlsx
@@ -9108,7 +9108,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119796718</v>
+        <v>119796715</v>
       </c>
       <c r="B79" t="n">
         <v>97930</v>
@@ -9152,10 +9152,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>728471</v>
+        <v>728459</v>
       </c>
       <c r="R79" t="n">
-        <v>7172510</v>
+        <v>7172400</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9219,7 +9219,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119796717</v>
+        <v>119796718</v>
       </c>
       <c r="B80" t="n">
         <v>97930</v>
@@ -9263,10 +9263,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>728451</v>
+        <v>728471</v>
       </c>
       <c r="R80" t="n">
-        <v>7172520</v>
+        <v>7172510</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9441,7 +9441,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119796720</v>
+        <v>119796721</v>
       </c>
       <c r="B82" t="n">
         <v>97930</v>
@@ -9485,10 +9485,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>728494</v>
+        <v>728587</v>
       </c>
       <c r="R82" t="n">
-        <v>7172550</v>
+        <v>7172540</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9552,7 +9552,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119796715</v>
+        <v>119796720</v>
       </c>
       <c r="B83" t="n">
         <v>97930</v>
@@ -9596,10 +9596,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>728459</v>
+        <v>728494</v>
       </c>
       <c r="R83" t="n">
-        <v>7172400</v>
+        <v>7172550</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9663,7 +9663,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119796716</v>
+        <v>119796714</v>
       </c>
       <c r="B84" t="n">
         <v>97930</v>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>728446</v>
+        <v>728468</v>
       </c>
       <c r="R84" t="n">
-        <v>7172530</v>
+        <v>7172390</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9774,7 +9774,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119796714</v>
+        <v>119796719</v>
       </c>
       <c r="B85" t="n">
         <v>97930</v>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>728468</v>
+        <v>728496</v>
       </c>
       <c r="R85" t="n">
-        <v>7172390</v>
+        <v>7172530</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9885,7 +9885,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119796721</v>
+        <v>119796717</v>
       </c>
       <c r="B86" t="n">
         <v>97930</v>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>728587</v>
+        <v>728451</v>
       </c>
       <c r="R86" t="n">
-        <v>7172540</v>
+        <v>7172520</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9996,7 +9996,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119796719</v>
+        <v>119796716</v>
       </c>
       <c r="B87" t="n">
         <v>97930</v>
@@ -10040,7 +10040,7 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>728496</v>
+        <v>728446</v>
       </c>
       <c r="R87" t="n">
         <v>7172530</v>

--- a/artfynd/A 44648-2020 artfynd.xlsx
+++ b/artfynd/A 44648-2020 artfynd.xlsx
@@ -3482,11 +3482,11 @@
         <v>117967026</v>
       </c>
       <c r="B27" t="n">
-        <v>57290</v>
+        <v>57384</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">

--- a/artfynd/A 44648-2020 artfynd.xlsx
+++ b/artfynd/A 44648-2020 artfynd.xlsx
@@ -3482,7 +3482,7 @@
         <v>117967026</v>
       </c>
       <c r="B27" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 44648-2020 artfynd.xlsx
+++ b/artfynd/A 44648-2020 artfynd.xlsx
@@ -3482,7 +3482,7 @@
         <v>117967026</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
